--- a/квартплата.xlsx
+++ b/квартплата.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">заезд</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t xml:space="preserve">март(плата за апрель)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">оплата за май</t>
   </si>
   <si>
     <t xml:space="preserve">гвс</t>
@@ -177,7 +180,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -204,10 +207,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -236,10 +235,11 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="13.93"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -262,11 +262,13 @@
       <c r="G1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="5"/>
+      <c r="H1" s="5" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="6" t="n">
@@ -287,7 +289,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="6" t="n">
@@ -308,7 +310,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="6" t="n">
@@ -329,7 +331,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="6" t="n">
@@ -350,7 +352,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="6" t="n">
@@ -371,7 +373,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="6" t="n">
@@ -392,7 +394,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="n">
@@ -407,13 +409,16 @@
       <c r="F8" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="7" t="n">
+        <v>850</v>
+      </c>
+      <c r="H8" s="0" t="n">
         <v>850</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="n">
@@ -439,7 +444,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="n">
@@ -453,7 +458,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>94000</v>
@@ -470,13 +475,16 @@
       <c r="F11" s="2" t="n">
         <v>47000</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="7" t="n">
+        <v>47000</v>
+      </c>
+      <c r="H11" s="0" t="n">
         <v>47000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>94000</v>
@@ -493,17 +501,20 @@
       <c r="F12" s="2" t="n">
         <v>48000</v>
       </c>
-      <c r="G12" s="8" t="n">
+      <c r="G12" s="7" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H12" s="0" t="n">
         <v>50000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="9" t="n">
-        <f aca="false">SUM(C12+D12+E12+F12+G12)-SUM(C11+D11+E11+F11+G11)-SUM(C10)</f>
-        <v>601.32</v>
+        <v>18</v>
+      </c>
+      <c r="B14" s="8" t="n">
+        <f aca="false">SUM(C12+D12+E12+F12+G12+H12)-SUM(C11+D11+E11+F11+G11+H11)-SUM(C10)</f>
+        <v>3601.32</v>
       </c>
     </row>
   </sheetData>

--- a/квартплата.xlsx
+++ b/квартплата.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t xml:space="preserve">заезд</t>
   </si>
@@ -41,6 +41,9 @@
   </si>
   <si>
     <t xml:space="preserve">оплата за май</t>
+  </si>
+  <si>
+    <t xml:space="preserve">за июнь</t>
   </si>
   <si>
     <t xml:space="preserve">гвс</t>
@@ -180,7 +183,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -202,6 +205,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -234,8 +241,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:I14"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.1"/>
@@ -265,136 +272,175 @@
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
+      <c r="I1" s="6" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="2"/>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="7" t="n">
         <v>573.24</v>
       </c>
-      <c r="D2" s="6" t="n">
+      <c r="D2" s="7" t="n">
         <v>770.09</v>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="7" t="n">
         <v>815.32</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>643.4</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="G2" s="8" t="n">
         <v>480.48</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>468.57</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <v>729.24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="7" t="n">
         <v>122.59</v>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>184.01</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="7" t="n">
         <v>204.64</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>154.27</v>
       </c>
-      <c r="G3" s="7" t="n">
+      <c r="G3" s="8" t="n">
         <v>124.17</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>108.74</v>
+      </c>
+      <c r="I3" s="0" t="n">
+        <v>176.63</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2"/>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="7" t="n">
         <v>27.56</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>26.2</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="7" t="n">
         <v>37.81</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>33.77</v>
       </c>
-      <c r="G4" s="7" t="n">
+      <c r="G4" s="8" t="n">
         <v>37.68</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <v>35.27</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2"/>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="7" t="n">
         <v>95.84</v>
       </c>
-      <c r="D5" s="6" t="n">
+      <c r="D5" s="7" t="n">
         <v>172.5</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="7" t="n">
         <v>217.68</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>170.53</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="8" t="n">
         <v>176.7</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>121.06</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>231.26</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="2"/>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="7" t="n">
         <v>91.77</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="7" t="n">
         <v>126.56</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="7" t="n">
         <v>158.03</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>142.52</v>
       </c>
-      <c r="G6" s="7" t="n">
+      <c r="G6" s="8" t="n">
         <v>121.75</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>91.92</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>143.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2"/>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="7" t="n">
         <v>1365.09</v>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="7" t="n">
         <v>1481.12</v>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="7" t="n">
         <v>1481.12</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1481.12</v>
       </c>
-      <c r="G7" s="7" t="n">
+      <c r="G7" s="8" t="n">
+        <v>1481.12</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>1481.12</v>
+      </c>
+      <c r="I7" s="0" t="n">
         <v>1481.12</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="n">
@@ -409,23 +455,26 @@
       <c r="F8" s="2" t="n">
         <v>850</v>
       </c>
-      <c r="G8" s="7" t="n">
+      <c r="G8" s="8" t="n">
         <v>850</v>
       </c>
       <c r="H8" s="0" t="n">
+        <v>850</v>
+      </c>
+      <c r="I8" s="0" t="n">
         <v>850</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="n">
         <f aca="false">SUM(C2:C8)</f>
         <v>3126.09</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="7" t="n">
         <f aca="false">SUM(D2:D8)</f>
         <v>3610.48</v>
       </c>
@@ -437,28 +486,36 @@
         <f aca="false">SUM(F2:F8)</f>
         <v>3475.61</v>
       </c>
-      <c r="G9" s="7" t="n">
+      <c r="G9" s="8" t="n">
         <f aca="false">SUM(G2:G8)</f>
         <v>3271.9</v>
       </c>
+      <c r="H9" s="0" t="n">
+        <f aca="false">SUM(H2:H8)</f>
+        <v>3141.74</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <f aca="false">SUM(I2:I8)</f>
+        <v>3646.72</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="n">
-        <f aca="false">SUM(C9+D9+E9+F9+G9)</f>
-        <v>17248.68</v>
+        <f aca="false">SUM(C9+D9+E9+F9+G9+H9+I9)</f>
+        <v>24037.14</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="7"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>94000</v>
@@ -475,16 +532,19 @@
       <c r="F11" s="2" t="n">
         <v>47000</v>
       </c>
-      <c r="G11" s="7" t="n">
+      <c r="G11" s="8" t="n">
         <v>47000</v>
       </c>
       <c r="H11" s="0" t="n">
+        <v>47000</v>
+      </c>
+      <c r="I11" s="0" t="n">
         <v>47000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>94000</v>
@@ -501,20 +561,23 @@
       <c r="F12" s="2" t="n">
         <v>48000</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="8" t="n">
         <v>50000</v>
       </c>
       <c r="H12" s="0" t="n">
         <v>50000</v>
       </c>
+      <c r="I12" s="0" t="n">
+        <v>50000</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="8" t="n">
-        <f aca="false">SUM(C12+D12+E12+F12+G12+H12)-SUM(C11+D11+E11+F11+G11+H11)-SUM(C10)</f>
-        <v>3601.32</v>
+        <v>19</v>
+      </c>
+      <c r="B14" s="9" t="n">
+        <f aca="false">SUM(C12+D12+E12+F12+G12+H12+I12)-SUM(C11+D11+E11+F11+G11+H11+I11)-SUM(C10)</f>
+        <v>-187.139999999999</v>
       </c>
     </row>
   </sheetData>

--- a/квартплата.xlsx
+++ b/квартплата.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t xml:space="preserve">заезд</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t xml:space="preserve">за июнь</t>
+  </si>
+  <si>
+    <t xml:space="preserve">за июль</t>
   </si>
   <si>
     <t xml:space="preserve">гвс</t>
@@ -91,7 +94,7 @@
     <numFmt numFmtId="165" formatCode="#,###.00"/>
     <numFmt numFmtId="166" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -119,6 +122,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -183,7 +191,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -218,6 +226,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -241,8 +253,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
-  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:J14"/>
+  <sheetFormatPr defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.1"/>
@@ -275,10 +287,13 @@
       <c r="I1" s="6" t="s">
         <v>7</v>
       </c>
+      <c r="J1" s="0" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="7" t="n">
@@ -302,10 +317,13 @@
       <c r="I2" s="0" t="n">
         <v>729.24</v>
       </c>
+      <c r="J2" s="0" t="n">
+        <v>489.72</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="7" t="n">
@@ -329,10 +347,13 @@
       <c r="I3" s="0" t="n">
         <v>176.63</v>
       </c>
+      <c r="J3" s="0" t="n">
+        <v>138.68</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="7" t="n">
@@ -356,10 +377,13 @@
       <c r="I4" s="0" t="n">
         <v>35.27</v>
       </c>
+      <c r="J4" s="0" t="n">
+        <v>26.51</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="7" t="n">
@@ -383,10 +407,13 @@
       <c r="I5" s="0" t="n">
         <v>231.26</v>
       </c>
+      <c r="J5" s="0" t="n">
+        <v>125.18</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="7" t="n">
@@ -410,10 +437,13 @@
       <c r="I6" s="0" t="n">
         <v>143.2</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J6" s="0" t="n">
+        <v>110.82</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="7" t="n">
@@ -437,10 +467,13 @@
       <c r="I7" s="0" t="n">
         <v>1481.12</v>
       </c>
+      <c r="J7" s="9" t="n">
+        <v>1481.12</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="n">
@@ -464,10 +497,13 @@
       <c r="I8" s="0" t="n">
         <v>850</v>
       </c>
+      <c r="J8" s="0" t="n">
+        <v>850</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="n">
@@ -498,15 +534,19 @@
         <f aca="false">SUM(I2:I8)</f>
         <v>3646.72</v>
       </c>
+      <c r="J9" s="0" t="n">
+        <f aca="false">SUM(J2:J8)</f>
+        <v>3222.03</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="n">
-        <f aca="false">SUM(C9+D9+E9+F9+G9+H9+I9)</f>
-        <v>24037.14</v>
+        <f aca="false">SUM(C9+D9+E9+F9+G9+H9+I9+J9)</f>
+        <v>27259.17</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
@@ -515,7 +555,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="2" t="n">
         <v>94000</v>
@@ -541,10 +581,13 @@
       <c r="I11" s="0" t="n">
         <v>47000</v>
       </c>
+      <c r="J11" s="0" t="n">
+        <v>47000</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>94000</v>
@@ -570,20 +613,23 @@
       <c r="I12" s="0" t="n">
         <v>50000</v>
       </c>
+      <c r="J12" s="0" t="n">
+        <v>50500</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="13.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="9" t="n">
-        <f aca="false">SUM(C12+D12+E12+F12+G12+H12+I12)-SUM(C11+D11+E11+F11+G11+H11+I11)-SUM(C10)</f>
-        <v>-187.139999999999</v>
+        <v>20</v>
+      </c>
+      <c r="B14" s="10" t="n">
+        <f aca="false">SUM(C12+D12+E12+F12+G12+H12+I12+J12)-SUM(C11+D11+E11+F11+G11+H11+I11+J11)-SUM(C10)</f>
+        <v>90.8300000000017</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.025" bottom="1.025" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader>&amp;C&amp;A</oddHeader>
     <oddFooter>&amp;CPage &amp;P</oddFooter>
